--- a/AAII_Financials/Quarterly/IESFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IESFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>IESFY</t>
   </si>
@@ -656,81 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +777,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,8 +824,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +871,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +892,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -923,8 +937,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,8 +984,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,8 +1031,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1055,8 +1078,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,8 +1096,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1114,8 +1141,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1158,8 +1188,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,8 +1209,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1220,8 +1254,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1264,8 +1301,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1308,8 +1348,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1352,8 +1395,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1396,8 +1442,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,8 +1489,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1484,8 +1536,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1528,8 +1583,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1630,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1677,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1724,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,8 +1771,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1748,8 +1818,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1792,8 +1865,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,8 +1912,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1880,57 +1959,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2032,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,404 +2051,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1083500</v>
+      </c>
+      <c r="E41" s="3">
         <v>991200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1170200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>985400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1189500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1343500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1075400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1128800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1273000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1051100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1129200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1066400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1445600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1107800</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>258300</v>
+      </c>
+      <c r="E42" s="3">
         <v>131700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>332200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>222600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>526500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>169600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>520900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>486000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>381900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>405500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>354000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>160000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>81500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>180900</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1864500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1836200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1624600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1591600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1617300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1459900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1509100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1394300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1547800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1601100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1497200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1568100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1544000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1430100</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E44" s="3">
         <v>45100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>42400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>48900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>44800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>40400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>41500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>47300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>44700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>58800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>47900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>43200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>42300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E45" s="3">
         <v>78300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>85300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>92300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>71500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>57600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>68000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>59400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>86300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>112100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>89000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>71600</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3334400</v>
+      </c>
+      <c r="E46" s="3">
         <v>3082500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3254700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2940800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3449700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3071000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3215000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3115900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3329300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3202800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3140000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2949800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3202300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2831100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1283300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1249900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1176700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1219500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1137300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1042200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1147100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1133000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1200200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1196900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1198900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1244900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1159400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1093600</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4509900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4250200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3901600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3748900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3640600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3513800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3587100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3575600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3722800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3681200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3513500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3382100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3125300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2988400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2653200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2635300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2577700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2589700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2596500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2591800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2633700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2648500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2650300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2732000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2697300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2709200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2677400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2627900</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2519,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,52 +2566,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6506500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5820500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5410000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5077200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4523700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4859900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4502300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4846600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4621200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4542800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4755700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4328200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4086000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2660,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22128400</v>
+      </c>
+      <c r="E54" s="3">
         <v>20962000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19720900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18876400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18745200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17460800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18383200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17765700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18501600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18383400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17985100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18061400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17308100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16244500</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2728,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,272 +2747,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>629300</v>
+      </c>
+      <c r="E57" s="3">
         <v>718700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>468100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>407000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>635300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>420200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>320600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>416500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>754800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>418500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>423200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>463000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>762500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>334900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>318100</v>
+      </c>
+      <c r="E58" s="3">
         <v>818000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>418600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>414500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>688300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>582200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>713500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>663000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>528100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>655100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1059200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>989700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>526000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>446000</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>241400</v>
+      </c>
+      <c r="E59" s="3">
         <v>255700</v>
       </c>
-      <c r="E59" s="3">
-        <v>188400</v>
-      </c>
       <c r="F59" s="3">
+        <v>255000</v>
+      </c>
+      <c r="G59" s="3">
         <v>211100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>281000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>206200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>276300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>241800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>276000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>201300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>285700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>245800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>259100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>290900</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1239600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1836800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1197500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1076100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1641800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1274800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1357900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1362500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1597800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1370000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1814000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1734700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1576600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1105900</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9694200</v>
+      </c>
+      <c r="E61" s="3">
         <v>8464400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8301100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8000600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7746800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7247800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7380900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7327900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7592400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7399000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6761500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6877800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7061500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6662600</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1047400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1009200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>915800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>887200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>877600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>820000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>870300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>873700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>889600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>920100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>863800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>909400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>847700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>798800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3074,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3121,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3168,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14089100</v>
+      </c>
+      <c r="E66" s="3">
         <v>13346000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12340600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11840700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12088100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11050300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11477300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11338200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11943200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11577400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11196700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11297200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11159300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10147600</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3236,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3281,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3328,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3375,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3422,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4718000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4237100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3978100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3656300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3451500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3443000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3503700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3316200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3371400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3511500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3255900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3033600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2584700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2696000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3516,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3563,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3610,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4973800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4672000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4527200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4306200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4079800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4047100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4198300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3939200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3936200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4203700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4088900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4072900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3733700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3803700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,57 +3704,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3608,8 +3803,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,52 +3824,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E83" s="3">
         <v>54700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>61600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>63900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>61100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>59200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>57700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>54100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>63100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>118700</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3916,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3963,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4010,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4057,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4104,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E89" s="3">
         <v>78400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>232200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>104900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>154500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>168000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>414400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>212800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>271700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>345400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>198100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>129000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>151300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,52 +4172,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-50400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-139100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-68300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-62200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-80900</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4264,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,52 +4311,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-235500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-63800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>280800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-333700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>255600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-51800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-145900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-73000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-121900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-214900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>134400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>30800</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,52 +4379,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E96" s="3">
         <v>85700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>10400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>241000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>166200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>101300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>279100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>18000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>16400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>356600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4471,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4518,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,136 +4565,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>162700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-303200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-592300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-93200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-252700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-283100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-39600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-93300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-85600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-481000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-173400</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-31100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>92000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-44000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>63100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-233400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-108700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-39500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>65900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>71800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-228900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>146100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-236300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-223100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>326800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-58700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>217600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-128100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-537300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>285700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>74600</v>
       </c>
     </row>
